--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.9743001757785</v>
+        <v>10.23332377856401</v>
       </c>
       <c r="D2" t="n">
-        <v>60.94671761026513</v>
+        <v>9.903841611668083</v>
       </c>
       <c r="E2" t="n">
-        <v>3.680535139501522</v>
+        <v>0.5980869601689971</v>
       </c>
       <c r="F2" t="n">
-        <v>3.857954170176789</v>
+        <v>0.6269175526537287</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.33537045478154</v>
+        <v>11.429497698902</v>
       </c>
       <c r="D3" t="n">
-        <v>68.6626259506187</v>
+        <v>11.15767671697554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.680535139501522</v>
+        <v>0.5980869601689971</v>
       </c>
       <c r="F3" t="n">
-        <v>3.857954170176789</v>
+        <v>0.6269175526537287</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
